--- a/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-07).xlsx
+++ b/dados_all_stores/KEYS Service Exceptions - All Stores (Stores) (2026-09-07).xlsx
@@ -935,34 +935,34 @@
     <t>214</t>
   </si>
   <si>
-    <t>24</t>
+    <t>19</t>
   </si>
   <si>
-    <t>R$ 8.421,42</t>
+    <t>R$ 8.356,54</t>
   </si>
   <si>
-    <t>92.2</t>
+    <t>91.5</t>
   </si>
   <si>
     <t>63.8</t>
   </si>
   <si>
-    <t>8.75</t>
+    <t>8.77</t>
   </si>
   <si>
-    <t>26.0</t>
+    <t>26.5</t>
   </si>
   <si>
-    <t>10.8</t>
+    <t>11.2</t>
   </si>
   <si>
     <t>6.4</t>
   </si>
   <si>
-    <t>24.1%</t>
+    <t>24.3%</t>
   </si>
   <si>
-    <t>19.2%</t>
+    <t>19.1%</t>
   </si>
   <si>
     <t>1.5%</t>
@@ -989,13 +989,13 @@
     <t>7.1%</t>
   </si>
   <si>
-    <t>2675.0</t>
+    <t>2676.0</t>
   </si>
   <si>
-    <t>2311.0</t>
+    <t>2312.0</t>
   </si>
   <si>
-    <t>182.0</t>
+    <t>183.0</t>
   </si>
   <si>
     <t>70.0</t>
@@ -5019,7 +5019,7 @@
         <v>19536</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>51</v>
@@ -5049,14 +5049,26 @@
         <v>58</v>
       </c>
       <c r="L24" s="4"/>
-      <c r="M24" s="5"/>
-      <c r="N24" s="6"/>
+      <c r="M24" s="5">
+        <v>7582.7399999999998</v>
+      </c>
+      <c r="N24" s="6">
+        <v>90</v>
+      </c>
       <c r="O24" s="6"/>
-      <c r="P24" s="7"/>
-      <c r="Q24" s="8"/>
-      <c r="R24" s="8"/>
+      <c r="P24" s="7">
+        <v>3.9284640449438206</v>
+      </c>
+      <c r="Q24" s="8">
+        <v>17.685333333333336</v>
+      </c>
+      <c r="R24" s="8">
+        <v>6.7811106666666667</v>
+      </c>
       <c r="S24" s="8"/>
-      <c r="T24" s="9"/>
+      <c r="T24" s="9">
+        <v>0.35999999999999999</v>
+      </c>
       <c r="U24" s="9"/>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
@@ -6843,7 +6855,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>51</v>
@@ -6873,14 +6885,26 @@
         <v>58</v>
       </c>
       <c r="L36" s="4"/>
-      <c r="M36" s="5"/>
-      <c r="N36" s="6"/>
+      <c r="M36" s="5">
+        <v>7354.4399999999996</v>
+      </c>
+      <c r="N36" s="6">
+        <v>84</v>
+      </c>
       <c r="O36" s="6"/>
-      <c r="P36" s="7"/>
-      <c r="Q36" s="8"/>
-      <c r="R36" s="8"/>
+      <c r="P36" s="7">
+        <v>12.623493975903614</v>
+      </c>
+      <c r="Q36" s="8">
+        <v>44.905411688311688</v>
+      </c>
+      <c r="R36" s="8">
+        <v>26.157777333333332</v>
+      </c>
       <c r="S36" s="8"/>
-      <c r="T36" s="9"/>
+      <c r="T36" s="9">
+        <v>0.23376623376623376</v>
+      </c>
       <c r="U36" s="9"/>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
@@ -9132,7 +9156,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>51</v>
@@ -9162,14 +9186,26 @@
         <v>58</v>
       </c>
       <c r="L51" s="4"/>
-      <c r="M51" s="5"/>
-      <c r="N51" s="6"/>
+      <c r="M51" s="5">
+        <v>1000.74</v>
+      </c>
+      <c r="N51" s="6">
+        <v>11</v>
+      </c>
       <c r="O51" s="6"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
+      <c r="P51" s="7">
+        <v>4.0888916666666661</v>
+      </c>
+      <c r="Q51" s="8">
+        <v>33.875</v>
+      </c>
+      <c r="R51" s="8">
+        <v>26.319042857142858</v>
+      </c>
       <c r="S51" s="8"/>
-      <c r="T51" s="9"/>
+      <c r="T51" s="9">
+        <v>0</v>
+      </c>
       <c r="U51" s="9"/>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
@@ -11830,7 +11866,7 @@
         <v>19647</v>
       </c>
       <c r="B69" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C69" s="4">
         <v>51</v>
@@ -11858,18 +11894,30 @@
         <v>58</v>
       </c>
       <c r="L69" s="4"/>
-      <c r="M69" s="5"/>
-      <c r="N69" s="6"/>
+      <c r="M69" s="5">
+        <v>6086.0299999999997</v>
+      </c>
+      <c r="N69" s="6">
+        <v>67</v>
+      </c>
       <c r="O69" s="6">
         <v>49</v>
       </c>
-      <c r="P69" s="7"/>
-      <c r="Q69" s="8"/>
-      <c r="R69" s="8"/>
+      <c r="P69" s="7">
+        <v>7.4921573529411765</v>
+      </c>
+      <c r="Q69" s="8">
+        <v>79.394218367346937</v>
+      </c>
+      <c r="R69" s="8">
+        <v>63.632312244897953</v>
+      </c>
       <c r="S69" s="8">
         <v>8</v>
       </c>
-      <c r="T69" s="9"/>
+      <c r="T69" s="9">
+        <v>0.040816326530612242</v>
+      </c>
       <c r="U69" s="9">
         <v>0.24489795918367346</v>
       </c>
@@ -14822,7 +14870,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>51</v>
@@ -14850,14 +14898,26 @@
         <v>58</v>
       </c>
       <c r="L89" s="4"/>
-      <c r="M89" s="5"/>
-      <c r="N89" s="6"/>
+      <c r="M89" s="5">
+        <v>7497.8400000000001</v>
+      </c>
+      <c r="N89" s="6">
+        <v>72</v>
+      </c>
       <c r="O89" s="6"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="8"/>
-      <c r="R89" s="8"/>
+      <c r="P89" s="7">
+        <v>19.541666216216218</v>
+      </c>
+      <c r="Q89" s="8">
+        <v>44.944871794871794</v>
+      </c>
+      <c r="R89" s="8">
+        <v>15.727927027027027</v>
+      </c>
       <c r="S89" s="8"/>
-      <c r="T89" s="9"/>
+      <c r="T89" s="9">
+        <v>0.076923076923076927</v>
+      </c>
       <c r="U89" s="9"/>
       <c r="V89" s="9"/>
       <c r="W89" s="9"/>
@@ -28478,7 +28538,9 @@
       <c r="N179" s="6">
         <v>125</v>
       </c>
-      <c r="O179" s="6"/>
+      <c r="O179" s="6">
+        <v>78</v>
+      </c>
       <c r="P179" s="7">
         <v>20.415873015873018</v>
       </c>
@@ -28488,31 +28550,75 @@
       <c r="R179" s="8">
         <v>7.747185714285715</v>
       </c>
-      <c r="S179" s="8"/>
+      <c r="S179" s="8">
+        <v>7</v>
+      </c>
       <c r="T179" s="9">
         <v>0.07792207792207792</v>
       </c>
-      <c r="U179" s="9"/>
-      <c r="V179" s="9"/>
-      <c r="W179" s="9"/>
-      <c r="X179" s="9"/>
-      <c r="Y179" s="9"/>
-      <c r="Z179" s="9"/>
-      <c r="AA179" s="9"/>
-      <c r="AB179" s="9"/>
-      <c r="AC179" s="9"/>
-      <c r="AD179" s="6"/>
-      <c r="AE179" s="6"/>
-      <c r="AF179" s="6"/>
-      <c r="AG179" s="6"/>
-      <c r="AH179" s="6"/>
-      <c r="AI179" s="6"/>
-      <c r="AJ179" s="6"/>
-      <c r="AK179" s="6"/>
-      <c r="AL179" s="6"/>
-      <c r="AM179" s="6"/>
-      <c r="AN179" s="9"/>
-      <c r="AO179" s="6"/>
+      <c r="U179" s="9">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="V179" s="9">
+        <v>0.01282051282051282</v>
+      </c>
+      <c r="W179" s="9">
+        <v>0</v>
+      </c>
+      <c r="X179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Y179" s="9">
+        <v>0</v>
+      </c>
+      <c r="Z179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AB179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AD179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AE179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AF179" s="6">
+        <v>1</v>
+      </c>
+      <c r="AG179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AH179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AI179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AL179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AM179" s="6">
+        <v>0</v>
+      </c>
+      <c r="AN179" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO179" s="6">
+        <v>0</v>
+      </c>
       <c t="s" r="AP179" s="4">
         <v>58</v>
       </c>
